--- a/InputData/indst/CRCC/Cement Overhaul Capital Cost per Unit Annual Capacity.xlsx
+++ b/InputData/indst/CRCC/Cement Overhaul Capital Cost per Unit Annual Capacity.xlsx
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>375</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>933</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>450</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>600</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -693,7 +693,7 @@
         <v/>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -711,7 +711,7 @@
         <v/>
       </c>
       <c r="D5" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -729,7 +729,7 @@
         <v/>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -747,7 +747,7 @@
         <v/>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -804,7 +804,7 @@
         <v/>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <f>IF(ABS(B4-C4)&lt;0.5,"PASS","FAIL")</f>
@@ -822,7 +822,7 @@
         <v/>
       </c>
       <c r="C5" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="D5">
         <f>IF(ABS(B5-C5)&lt;0.5,"PASS","FAIL")</f>
@@ -840,7 +840,7 @@
         <v/>
       </c>
       <c r="C6" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <f>IF(ABS(B6-C6)&lt;0.5,"PASS","FAIL")</f>
@@ -858,7 +858,7 @@
         <v/>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <f>IF(ABS(B7-C7)&lt;0.5,"PASS","FAIL")</f>
@@ -894,7 +894,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unit: $/(metric ton/yr) overhaul (EI judgment ~10% of greenfield; no public source exists - see generator comments)</t>
+          <t>Unit: $/(metric ton/yr) overhaul, 2012 USD (EI judgment ~10% of greenfield CPCC; research 2026-10-01 range 5-20%; follows the CPCC dollar-year fix)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
